--- a/public/downloads/SkafteSelective2019.xlsx
+++ b/public/downloads/SkafteSelective2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>CO</t>
@@ -659,10 +682,10 @@
         <v>41</v>
       </c>
       <c r="N3" s="5">
-        <v>723.4193246364594</v>
+        <v>723419.3246364594</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03251468940790415</v>
+        <v>32.51468940790415</v>
       </c>
       <c r="P3" s="5">
         <v>22249</v>
@@ -709,10 +732,10 @@
         <v>41</v>
       </c>
       <c r="N4" s="5">
-        <v>297.5777263641357</v>
+        <v>297577.7263641357</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04777295334148912</v>
+        <v>47.77295334148912</v>
       </c>
       <c r="P4" s="5">
         <v>6229</v>
@@ -759,10 +782,10 @@
         <v>41</v>
       </c>
       <c r="N5" s="5">
-        <v>931.2928190231323</v>
+        <v>931292.8190231323</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1466141087882765</v>
+        <v>146.6141087882765</v>
       </c>
       <c r="P5" s="5">
         <v>6352</v>
@@ -809,10 +832,10 @@
         <v>41</v>
       </c>
       <c r="N6" s="5">
-        <v>489.6474764347076</v>
+        <v>489647.4764347076</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08484620974436105</v>
+        <v>84.84620974436105</v>
       </c>
       <c r="P6" s="5">
         <v>5771</v>
@@ -859,10 +882,10 @@
         <v>41</v>
       </c>
       <c r="N7" s="5">
-        <v>1962.52992105484</v>
+        <v>1962529.92105484</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1684719650660864</v>
+        <v>168.4719650660864</v>
       </c>
       <c r="P7" s="5">
         <v>11649</v>
@@ -909,10 +932,10 @@
         <v>41</v>
       </c>
       <c r="N8" s="5">
-        <v>135.1817221641541</v>
+        <v>135181.7221641541</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01225582249901669</v>
+        <v>12.25582249901669</v>
       </c>
       <c r="P8" s="5">
         <v>11030</v>
@@ -959,10 +982,10 @@
         <v>41</v>
       </c>
       <c r="N9" s="5">
-        <v>346.9236414432526</v>
+        <v>346923.6414432526</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02833417522404872</v>
+        <v>28.33417522404872</v>
       </c>
       <c r="P9" s="5">
         <v>12244</v>
@@ -1009,10 +1032,10 @@
         <v>41</v>
       </c>
       <c r="N10" s="5">
-        <v>475.1932117938995</v>
+        <v>475193.2117938995</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08117410519198831</v>
+        <v>81.1741051919883</v>
       </c>
       <c r="P10" s="5">
         <v>5854</v>
@@ -1059,10 +1082,10 @@
         <v>41</v>
       </c>
       <c r="N11" s="5">
-        <v>615.3034598827362</v>
+        <v>615303.4598827362</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03778808941121023</v>
+        <v>37.78808941121023</v>
       </c>
       <c r="P11" s="5">
         <v>16283</v>
@@ -1109,10 +1132,10 @@
         <v>41</v>
       </c>
       <c r="N12" s="5">
-        <v>170.6490564346313</v>
+        <v>170649.0564346313</v>
       </c>
       <c r="O12" s="4">
-        <v>0.0176655337924049</v>
+        <v>17.6655337924049</v>
       </c>
       <c r="P12" s="5">
         <v>9660</v>
@@ -1159,10 +1182,10 @@
         <v>41</v>
       </c>
       <c r="N13" s="5">
-        <v>745.0464532375336</v>
+        <v>745046.4532375336</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07221541661699463</v>
+        <v>72.21541661699463</v>
       </c>
       <c r="P13" s="5">
         <v>10317</v>
@@ -1209,10 +1232,10 @@
         <v>33</v>
       </c>
       <c r="N14" s="5">
-        <v>1242.691427946091</v>
+        <v>1242691.427946091</v>
       </c>
       <c r="O14" s="4">
-        <v>0.2429504257959122</v>
+        <v>242.9504257959122</v>
       </c>
       <c r="P14" s="5">
         <v>5115</v>
@@ -1259,10 +1282,10 @@
         <v>33</v>
       </c>
       <c r="N15" s="5">
-        <v>1425.077337503433</v>
+        <v>1425077.337503433</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2310436669104139</v>
+        <v>231.0436669104139</v>
       </c>
       <c r="P15" s="5">
         <v>6168</v>
@@ -1309,10 +1332,10 @@
         <v>33</v>
       </c>
       <c r="N16" s="5">
-        <v>642.4225540161133</v>
+        <v>642422.5540161133</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09844047717071917</v>
+        <v>98.44047717071918</v>
       </c>
       <c r="P16" s="5">
         <v>6526</v>
@@ -1359,10 +1382,10 @@
         <v>33</v>
       </c>
       <c r="N17" s="5">
-        <v>1087.210937023163</v>
+        <v>1087210.937023163</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1006490406427664</v>
+        <v>100.6490406427664</v>
       </c>
       <c r="P17" s="5">
         <v>10802</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,75 +1497,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.494339892946302</v>
+        <v>0.5546534861996736</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4673762379258266</v>
+        <v>0.1275346260450798</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6354424486641883</v>
+        <v>2.795487873115705</v>
       </c>
       <c r="E3" s="4">
-        <v>79.83418367346938</v>
+        <v>71.33928571428571</v>
       </c>
       <c r="F3" s="4">
-        <v>76.2751677852349</v>
+        <v>67.09731543624162</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1275346260450798</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5595526206323549</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07356558188790246</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2591095990441872</v>
+        <v>0.218374692736543</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2210139347653358</v>
+        <v>0.2209108644879962</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3031649366540161</v>
+        <v>5.028490297993985</v>
       </c>
       <c r="E4" s="4">
-        <v>76.77248677248673</v>
+        <v>73.03854875283518</v>
       </c>
       <c r="F4" s="4">
-        <v>74.51901565995497</v>
+        <v>68.79194630872642</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>2</v>
@@ -1542,50 +1615,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.198243643784167</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1911920356718547</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1185862913919436</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.250778029474907</v>
+        <v>0.6788008453607972</v>
       </c>
       <c r="C5" s="4">
-        <v>1.06251081608079</v>
+        <v>0.7522811046844922</v>
       </c>
       <c r="D5" s="4">
-        <v>1.555393122851189</v>
+        <v>0.8429918240920651</v>
       </c>
       <c r="E5" s="4">
-        <v>74.96173469387755</v>
+        <v>76.56887755102041</v>
       </c>
       <c r="F5" s="4">
-        <v>69.40855704697987</v>
+        <v>71.24580536912751</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.5224219946696493</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7573665444400008</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6031848271278761</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,40 +1797,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>3.72693753536148</v>
+        <v>0.50729527148986</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2716804629835167</v>
+        <v>0.6152578854604004</v>
       </c>
       <c r="D3" s="4">
-        <v>6.354333463267516</v>
+        <v>0.5727161581137006</v>
       </c>
       <c r="E3" s="4">
-        <v>76.43494897959187</v>
+        <v>82.66581632653062</v>
       </c>
       <c r="F3" s="4">
-        <v>74.8559843400448</v>
+        <v>78.55914429530202</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
@@ -1714,91 +1856,143 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4925250895619714</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6068917466739844</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.657607212986106</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>4.515324782241753</v>
+        <v>0.1892218701600683</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2397043029804649</v>
+        <v>0.15473461782067</v>
       </c>
       <c r="D4" s="4">
-        <v>7.066346549498688</v>
+        <v>0.8365301432210228</v>
       </c>
       <c r="E4" s="4">
-        <v>74.56916099773295</v>
+        <v>74.08541194255454</v>
       </c>
       <c r="F4" s="4">
-        <v>70.5443698732302</v>
+        <v>72.90206313696191</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.15473461782067</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1698206083412786</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09984362212237367</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.214219969628267</v>
+        <v>0.7486654158263883</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6865651833597143</v>
+        <v>0.4506466197015335</v>
       </c>
       <c r="D5" s="4">
-        <v>1.559070748207978</v>
+        <v>1.298851849519317</v>
       </c>
       <c r="E5" s="4">
-        <v>77.28741496598639</v>
+        <v>70.66964285714288</v>
       </c>
       <c r="F5" s="4">
-        <v>70.09088366890381</v>
+        <v>59.70637583892611</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7486654158263883</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4506466197015335</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2003,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2022,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2064,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,81 +2095,117 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.669192668579094</v>
+        <v>0.494339892946302</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1138028825378257</v>
+        <v>0.4673762379258266</v>
       </c>
       <c r="D3" s="4">
-        <v>3.880667490194086</v>
+        <v>0.6354424486641883</v>
       </c>
       <c r="E3" s="4">
-        <v>74.34523809523793</v>
+        <v>79.83418367346938</v>
       </c>
       <c r="F3" s="4">
-        <v>67.13856263982177</v>
+        <v>76.2751677852349</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4673762379258266</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2242874742260578</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.234207870768081</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>3.002005342883572</v>
+        <v>0.2591095990441872</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1624479095478478</v>
+        <v>0.2210139347653358</v>
       </c>
       <c r="D4" s="4">
-        <v>5.369345845177386</v>
+        <v>0.3031649366540161</v>
       </c>
       <c r="E4" s="4">
-        <v>75.38548752834512</v>
+        <v>76.77248677248673</v>
       </c>
       <c r="F4" s="4">
-        <v>69.20333084762702</v>
+        <v>74.51901565995497</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>2</v>
@@ -1968,50 +2213,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.0869762100861043</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2653238145317392</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2158392229823131</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.084311646340303</v>
+        <v>1.250778029474907</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5650151256823488</v>
+        <v>1.06251081608079</v>
       </c>
       <c r="D5" s="4">
-        <v>1.385008496163301</v>
+        <v>1.555393122851189</v>
       </c>
       <c r="E5" s="4">
-        <v>77.9613095238096</v>
+        <v>74.96173469387755</v>
       </c>
       <c r="F5" s="4">
-        <v>71.03956935123163</v>
+        <v>69.40855704697987</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>1.06251081608079</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5510188920913042</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4836689049295833</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2303,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2322,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2364,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,66 +2395,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5516117099568172</v>
+        <v>3.72693753536148</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1379945617660496</v>
+        <v>0.2716804629835167</v>
       </c>
       <c r="D3" s="4">
-        <v>4.699377051995847</v>
+        <v>6.354333463267516</v>
       </c>
       <c r="E3" s="4">
-        <v>71.62202380952407</v>
+        <v>76.43494897959187</v>
       </c>
       <c r="F3" s="4">
-        <v>67.68246644295377</v>
+        <v>74.8559843400448</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2601089157362083</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>3.563962218470695</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.166985305399985</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2819626579682175</v>
+        <v>4.515324782241753</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2351595275400427</v>
+        <v>0.2397043029804649</v>
       </c>
       <c r="D4" s="4">
-        <v>7.171311789949538</v>
+        <v>7.066346549498688</v>
       </c>
       <c r="E4" s="4">
-        <v>72.17687074830005</v>
+        <v>74.56916099773295</v>
       </c>
       <c r="F4" s="4">
-        <v>68.7173750932148</v>
+        <v>70.5443698732302</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2167,51 +2499,69 @@
         <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1642231953086252</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>4.533571803942711</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2068596639187399</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8452886032409515</v>
+        <v>1.214219969628267</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5335763651177938</v>
+        <v>0.6865651833597143</v>
       </c>
       <c r="D5" s="4">
-        <v>1.129074257729463</v>
+        <v>1.559070748207978</v>
       </c>
       <c r="E5" s="4">
-        <v>76.40093537414965</v>
+        <v>77.28741496598639</v>
       </c>
       <c r="F5" s="4">
-        <v>66.14024049217002</v>
+        <v>70.09088366890381</v>
       </c>
       <c r="G5" s="5">
         <v>16</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -2220,11 +2570,29 @@
         <v>8</v>
       </c>
       <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.7673232780566241</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8147759014379812</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6790787479656983</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2603,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2611,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2622,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2664,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,66 +2695,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7939506296517537</v>
+        <v>1.669192668579094</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5665601789473584</v>
+        <v>0.1138028825378257</v>
       </c>
       <c r="D3" s="4">
-        <v>0.8785475168826268</v>
+        <v>3.880667490194086</v>
       </c>
       <c r="E3" s="4">
-        <v>78.6203231292517</v>
+        <v>74.34523809523793</v>
       </c>
       <c r="F3" s="4">
-        <v>74.20441834451903</v>
+        <v>67.13856263982177</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01423300036377384</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.663855293442679</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1138028825378257</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4944077275163323</v>
+        <v>3.002005342883572</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4118459751901639</v>
+        <v>0.1624479095478478</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5557466489043416</v>
+        <v>5.369345845177386</v>
       </c>
       <c r="E4" s="4">
-        <v>75.58956916099774</v>
+        <v>75.38548752834512</v>
       </c>
       <c r="F4" s="4">
-        <v>70.83271190653706</v>
+        <v>69.20333084762702</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2386,58 +2805,94 @@
         <v>3</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.001976872676789298</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.002224995403215</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1620525350124899</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.715256997947892</v>
+        <v>1.084311646340303</v>
       </c>
       <c r="C5" s="4">
-        <v>1.347684931307191</v>
+        <v>0.5650151256823488</v>
       </c>
       <c r="D5" s="4">
-        <v>2.136951919004647</v>
+        <v>1.385008496163301</v>
       </c>
       <c r="E5" s="4">
-        <v>64.87244897959182</v>
+        <v>77.9613095238096</v>
       </c>
       <c r="F5" s="4">
-        <v>55.32158836689037</v>
+        <v>71.03956935123163</v>
       </c>
       <c r="G5" s="5">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5">
         <v>8</v>
       </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4917722927258001</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7369000408108413</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3619642073492262</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2903,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2911,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2922,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2964,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2995,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2333972299151633</v>
+        <v>0.5516117099568172</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2136635870551809</v>
+        <v>0.1379945617660496</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3820116845792441</v>
+        <v>4.699377051995847</v>
       </c>
       <c r="E3" s="4">
-        <v>84.20918367346938</v>
+        <v>71.62202380952407</v>
       </c>
       <c r="F3" s="4">
-        <v>79.79725950782998</v>
+        <v>67.68246644295377</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1286653207879596</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5994693899731347</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1050446010107251</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7412961809625737</v>
+        <v>0.2819626579682175</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8272885743693986</v>
+        <v>0.2351595275400427</v>
       </c>
       <c r="D4" s="4">
-        <v>4.02292647349742</v>
+        <v>7.171311789949538</v>
       </c>
       <c r="E4" s="4">
-        <v>79.7278911564631</v>
+        <v>72.17687074830005</v>
       </c>
       <c r="F4" s="4">
-        <v>78.15684812329123</v>
+        <v>68.7173750932148</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2236664783896799</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2370267869895748</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.189961300362479</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.046883353323035</v>
+        <v>0.8452886032409515</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5833884882716007</v>
+        <v>0.5335763651177938</v>
       </c>
       <c r="D5" s="4">
-        <v>1.337551947042672</v>
+        <v>1.129074257729463</v>
       </c>
       <c r="E5" s="4">
-        <v>75.91411564625845</v>
+        <v>76.40093537414965</v>
       </c>
       <c r="F5" s="4">
-        <v>67.12388143176699</v>
+        <v>66.14024049217002</v>
       </c>
       <c r="G5" s="5">
+        <v>16</v>
+      </c>
+      <c r="H5" s="5">
         <v>8</v>
       </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3038566337695148</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7034498041668624</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4777912422967519</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3203,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3211,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3222,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3264,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,66 +3295,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9179212635498405</v>
+        <v>0.7939506296517537</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3493583368565378</v>
+        <v>0.5665601789473584</v>
       </c>
       <c r="D3" s="4">
-        <v>0.61695015900336</v>
+        <v>0.8785475168826268</v>
       </c>
       <c r="E3" s="4">
-        <v>65.46130952380952</v>
+        <v>78.6203231292517</v>
       </c>
       <c r="F3" s="4">
-        <v>61.50447427293064</v>
+        <v>74.20441834451903</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5665601789473584</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4784178210246289</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4016437925123739</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4257503984464282</v>
+        <v>0.4944077275163323</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3543898202369234</v>
+        <v>0.4118459751901639</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4934540068407769</v>
+        <v>0.5557466489043416</v>
       </c>
       <c r="E4" s="4">
-        <v>73.26908541194253</v>
+        <v>75.58956916099774</v>
       </c>
       <c r="F4" s="4">
-        <v>66.33109619686749</v>
+        <v>70.83271190653706</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
@@ -2820,37 +3413,55 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4118459751901639</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3475909820761776</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3102260434748837</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.392346086155572</v>
+        <v>1.715256997947892</v>
       </c>
       <c r="C5" s="4">
-        <v>0.9477859343333339</v>
+        <v>1.347684931307191</v>
       </c>
       <c r="D5" s="4">
-        <v>1.306184241180612</v>
+        <v>2.136951919004647</v>
       </c>
       <c r="E5" s="4">
-        <v>63.12074829931972</v>
+        <v>64.87244897959182</v>
       </c>
       <c r="F5" s="4">
-        <v>55.94239373601789</v>
+        <v>55.32158836689037</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -2859,11 +3470,27 @@
         <v>5</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.715256997947892</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.347684931307191</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3501,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3509,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3520,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3562,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,40 +3593,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4111598647625357</v>
+        <v>0.2333972299151633</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3816923304410648</v>
+        <v>0.2136635870551809</v>
       </c>
       <c r="D3" s="4">
-        <v>1.892350470782927</v>
+        <v>0.3820116845792441</v>
       </c>
       <c r="E3" s="4">
-        <v>80.80994897959177</v>
+        <v>84.20918367346938</v>
       </c>
       <c r="F3" s="4">
-        <v>76.8148769574957</v>
+        <v>79.79725950782998</v>
       </c>
       <c r="G3" s="5">
         <v>16</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>2</v>
@@ -2992,91 +3652,143 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0921983054230433</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2426243066497177</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.198297202818007</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.967254834843314</v>
+        <v>0.7412961809625737</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3508204352797634</v>
+        <v>0.8272885743693986</v>
       </c>
       <c r="D4" s="4">
-        <v>6.08503819260309</v>
+        <v>4.02292647349742</v>
       </c>
       <c r="E4" s="4">
-        <v>73.36734693877558</v>
+        <v>79.7278911564631</v>
       </c>
       <c r="F4" s="4">
-        <v>69.81108625404066</v>
+        <v>78.15684812329123</v>
       </c>
       <c r="G4" s="5">
         <v>9</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.8272885743693986</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3230764246175374</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1641103523509243</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.501562091812818</v>
+        <v>1.046883353323035</v>
       </c>
       <c r="C5" s="4">
-        <v>1.141745969605124</v>
+        <v>0.5833884882716007</v>
       </c>
       <c r="D5" s="4">
-        <v>1.812125529453478</v>
+        <v>1.337551947042672</v>
       </c>
       <c r="E5" s="4">
-        <v>78.7202380952381</v>
+        <v>75.91411564625845</v>
       </c>
       <c r="F5" s="4">
-        <v>73.29418344519016</v>
+        <v>67.12388143176699</v>
       </c>
       <c r="G5" s="5">
         <v>8</v>
       </c>
       <c r="H5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.046883353323035</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5833884882716007</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3799,1468 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9179212635498405</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3493583368565378</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.61695015900336</v>
+      </c>
+      <c r="E3" s="4">
+        <v>65.46130952380952</v>
+      </c>
+      <c r="F3" s="4">
+        <v>61.50447427293064</v>
+      </c>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5">
+        <v>8</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>8</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>8</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.2667579539594396</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9523483333963926</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2848334995699222</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4257503984464282</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3543898202369234</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4934540068407769</v>
+      </c>
+      <c r="E4" s="4">
+        <v>73.26908541194253</v>
+      </c>
+      <c r="F4" s="4">
+        <v>66.33109619686749</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1773509606084815</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3151944806798361</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2827980120036523</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.392346086155572</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.9477859343333339</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.306184241180612</v>
+      </c>
+      <c r="E5" s="4">
+        <v>63.12074829931972</v>
+      </c>
+      <c r="F5" s="4">
+        <v>55.94239373601789</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>6</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.392346086155572</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9477859343333339</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4111598647625357</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3816923304410648</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1.892350470782927</v>
+      </c>
+      <c r="E3" s="4">
+        <v>80.80994897959177</v>
+      </c>
+      <c r="F3" s="4">
+        <v>76.8148769574957</v>
+      </c>
+      <c r="G3" s="5">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>3</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.3725492984602011</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2288238386116149</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2469265023820767</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.967254834843314</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3508204352797634</v>
+      </c>
+      <c r="D4" s="4">
+        <v>6.08503819260309</v>
+      </c>
+      <c r="E4" s="4">
+        <v>73.36734693877558</v>
+      </c>
+      <c r="F4" s="4">
+        <v>69.81108625404066</v>
+      </c>
+      <c r="G4" s="5">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5">
+        <v>5</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3508204352797634</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.880759452613775</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.177889908746015</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.501562091812818</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.141745969605124</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.812125529453478</v>
+      </c>
+      <c r="E5" s="4">
+        <v>78.7202380952381</v>
+      </c>
+      <c r="F5" s="4">
+        <v>73.29418344519016</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8</v>
+      </c>
+      <c r="H5" s="5">
+        <v>5</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>3</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>1.286484203261678</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5329768320685104</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4238652580231612</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>43.90243902439025</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.439024390243902</v>
+      </c>
+      <c r="D3" s="3">
+        <v>53.65853658536586</v>
+      </c>
+      <c r="E3" s="3">
+        <v>12.19512195121951</v>
+      </c>
+      <c r="F3" s="3">
+        <v>41.46341463414634</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2.455552478036258</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.2390065072458856</v>
+      </c>
+      <c r="J3" s="4">
+        <v>4.034094494716774</v>
+      </c>
+      <c r="K3" s="4">
+        <v>73.96963663514177</v>
+      </c>
+      <c r="L3" s="4">
+        <v>68.03350248267478</v>
+      </c>
+      <c r="M3" s="5">
+        <v>41</v>
+      </c>
+      <c r="N3" s="5">
+        <v>723419.3246364594</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.51468940790415</v>
+      </c>
+      <c r="P3" s="5">
+        <v>22249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>63.41463414634146</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7.317073170731707</v>
+      </c>
+      <c r="D4" s="3">
+        <v>29.26829268292683</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>29.26829268292683</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.4539486345274115</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3830034136638982</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.7375590147229617</v>
+      </c>
+      <c r="K4" s="4">
+        <v>77.34942757590836</v>
+      </c>
+      <c r="L4" s="4">
+        <v>73.50466524799332</v>
+      </c>
+      <c r="M4" s="5">
+        <v>41</v>
+      </c>
+      <c r="N4" s="5">
+        <v>297577.7263641357</v>
+      </c>
+      <c r="O4" s="4">
+        <v>47.77295334148912</v>
+      </c>
+      <c r="P4" s="5">
+        <v>6229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>60.97560975609756</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>39.02439024390244</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>39.02439024390244</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5682454598824628</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1985196039922694</v>
+      </c>
+      <c r="J5" s="4">
+        <v>1.571098460170015</v>
+      </c>
+      <c r="K5" s="4">
+        <v>76.78944748631179</v>
+      </c>
+      <c r="L5" s="4">
+        <v>72.26523708190115</v>
+      </c>
+      <c r="M5" s="5">
+        <v>41</v>
+      </c>
+      <c r="N5" s="5">
+        <v>931292.8190231323</v>
+      </c>
+      <c r="O5" s="4">
+        <v>146.6141087882765</v>
+      </c>
+      <c r="P5" s="5">
+        <v>6352</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>63.41463414634146</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4.878048780487805</v>
+      </c>
+      <c r="D6" s="3">
+        <v>31.70731707317073</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>31.70731707317073</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.7574778376233756</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.6390924584244746</v>
+      </c>
+      <c r="J6" s="4">
+        <v>1.309789066683013</v>
+      </c>
+      <c r="K6" s="4">
+        <v>77.28554836568769</v>
+      </c>
+      <c r="L6" s="4">
+        <v>72.96175042287393</v>
+      </c>
+      <c r="M6" s="5">
+        <v>41</v>
+      </c>
+      <c r="N6" s="5">
+        <v>489647.4764347076</v>
+      </c>
+      <c r="O6" s="4">
+        <v>84.84620974436105</v>
+      </c>
+      <c r="P6" s="5">
+        <v>5771</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>34.14634146341464</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9.75609756097561</v>
+      </c>
+      <c r="D7" s="3">
+        <v>56.09756097560976</v>
+      </c>
+      <c r="E7" s="3">
+        <v>7.317073170731707</v>
+      </c>
+      <c r="F7" s="3">
+        <v>29.26829268292683</v>
+      </c>
+      <c r="G7" s="3">
+        <v>19.51219512195122</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.371948345251445</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.1194439416629385</v>
+      </c>
+      <c r="J7" s="4">
+        <v>3.639662509654689</v>
+      </c>
+      <c r="K7" s="4">
+        <v>75.65621370499423</v>
+      </c>
+      <c r="L7" s="4">
+        <v>69.39324493916119</v>
+      </c>
+      <c r="M7" s="5">
+        <v>41</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1962529.92105484</v>
+      </c>
+      <c r="O7" s="4">
+        <v>168.4719650660864</v>
+      </c>
+      <c r="P7" s="5">
+        <v>11649</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>51.21951219512195</v>
+      </c>
+      <c r="C8" s="3">
+        <v>24.39024390243902</v>
+      </c>
+      <c r="D8" s="3">
+        <v>24.39024390243902</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>24.39024390243902</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.555888657614741</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.2860445109088546</v>
+      </c>
+      <c r="J8" s="4">
+        <v>2.646046105136394</v>
+      </c>
+      <c r="K8" s="4">
+        <v>73.75311100049855</v>
+      </c>
+      <c r="L8" s="4">
+        <v>69.08823047962106</v>
+      </c>
+      <c r="M8" s="5">
+        <v>41</v>
+      </c>
+      <c r="N8" s="5">
+        <v>135181.7221641541</v>
+      </c>
+      <c r="O8" s="4">
+        <v>12.25582249901669</v>
+      </c>
+      <c r="P8" s="5">
+        <v>11030</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>53.65853658536586</v>
+      </c>
+      <c r="C9" s="3">
+        <v>7.317073170731707</v>
+      </c>
+      <c r="D9" s="3">
+        <v>39.02439024390244</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7.317073170731707</v>
+      </c>
+      <c r="F9" s="3">
+        <v>31.70731707317073</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.5662756115872554</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.4678606712442567</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.9109686107614557</v>
+      </c>
+      <c r="K9" s="4">
+        <v>76.10087937614088</v>
+      </c>
+      <c r="L9" s="4">
+        <v>69.9601680580557</v>
+      </c>
+      <c r="M9" s="5">
+        <v>41</v>
+      </c>
+      <c r="N9" s="5">
+        <v>346923.6414432526</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.33417522404872</v>
+      </c>
+      <c r="P9" s="5">
+        <v>12244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>73.17073170731707</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.439024390243902</v>
+      </c>
+      <c r="D10" s="3">
+        <v>24.39024390243902</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>24.39024390243902</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3608003949234987</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3303185548755284</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3895822242411092</v>
+      </c>
+      <c r="K10" s="4">
+        <v>77.26066036170512</v>
+      </c>
+      <c r="L10" s="4">
+        <v>73.21001800621828</v>
+      </c>
+      <c r="M10" s="5">
+        <v>41</v>
+      </c>
+      <c r="N10" s="5">
+        <v>475193.2117938995</v>
+      </c>
+      <c r="O10" s="4">
+        <v>81.1741051919883</v>
+      </c>
+      <c r="P10" s="5">
+        <v>5854</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>56.09756097560976</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>43.90243902439025</v>
+      </c>
+      <c r="E11" s="3">
+        <v>12.19512195121951</v>
+      </c>
+      <c r="F11" s="3">
+        <v>31.70731707317073</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>2.703950150098127</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3537731024921364</v>
+      </c>
+      <c r="J11" s="4">
+        <v>4.352247727099993</v>
+      </c>
+      <c r="K11" s="4">
+        <v>76.3580554172886</v>
+      </c>
+      <c r="L11" s="4">
+        <v>72.04998090249407</v>
+      </c>
+      <c r="M11" s="5">
+        <v>41</v>
+      </c>
+      <c r="N11" s="5">
+        <v>615303.4598827362</v>
+      </c>
+      <c r="O11" s="4">
+        <v>37.78808941121023</v>
+      </c>
+      <c r="P11" s="5">
+        <v>16283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>51.21951219512195</v>
+      </c>
+      <c r="C12" s="3">
+        <v>9.75609756097561</v>
+      </c>
+      <c r="D12" s="3">
+        <v>39.02439024390244</v>
+      </c>
+      <c r="E12" s="3">
+        <v>12.19512195121951</v>
+      </c>
+      <c r="F12" s="3">
+        <v>26.82926829268293</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1.595905129431348</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2198285425789935</v>
+      </c>
+      <c r="J12" s="4">
+        <v>3.091377556772224</v>
+      </c>
+      <c r="K12" s="4">
+        <v>75.98473535755741</v>
+      </c>
+      <c r="L12" s="4">
+        <v>69.11414852403557</v>
+      </c>
+      <c r="M12" s="5">
+        <v>41</v>
+      </c>
+      <c r="N12" s="5">
+        <v>170649.0564346313</v>
+      </c>
+      <c r="O12" s="4">
+        <v>17.6655337924049</v>
+      </c>
+      <c r="P12" s="5">
+        <v>9660</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>51.21951219512195</v>
+      </c>
+      <c r="C13" s="3">
+        <v>9.75609756097561</v>
+      </c>
+      <c r="D13" s="3">
+        <v>39.02439024390244</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4.878048780487805</v>
+      </c>
+      <c r="F13" s="3">
+        <v>34.14634146341464</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.560486541198686</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2672615832510576</v>
+      </c>
+      <c r="J13" s="4">
+        <v>3.794292500306187</v>
+      </c>
+      <c r="K13" s="4">
+        <v>73.60876057740143</v>
+      </c>
+      <c r="L13" s="4">
+        <v>67.30779723904585</v>
+      </c>
+      <c r="M13" s="5">
+        <v>41</v>
+      </c>
+      <c r="N13" s="5">
+        <v>745046.4532375336</v>
+      </c>
+      <c r="O13" s="4">
+        <v>72.21541661699463</v>
+      </c>
+      <c r="P13" s="5">
+        <v>10317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>54.54545454545454</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D14" s="3">
+        <v>42.42424242424242</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>42.42424242424242</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.7425775745049332</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.5339234964677629</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.8930753654426814</v>
+      </c>
+      <c r="K14" s="4">
+        <v>74.46093588950696</v>
+      </c>
+      <c r="L14" s="4">
+        <v>68.70720629109879</v>
+      </c>
+      <c r="M14" s="5">
+        <v>33</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1242691.427946091</v>
+      </c>
+      <c r="O14" s="4">
+        <v>242.9504257959122</v>
+      </c>
+      <c r="P14" s="5">
+        <v>5115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>69.6969696969697</v>
+      </c>
+      <c r="C15" s="3">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="D15" s="3">
+        <v>24.24242424242424</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="F15" s="3">
+        <v>21.21212121212121</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.4595376834708365</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2548649066677807</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1.515233873547921</v>
+      </c>
+      <c r="K15" s="4">
+        <v>80.9760874046584</v>
+      </c>
+      <c r="L15" s="4">
+        <v>76.27754050572827</v>
+      </c>
+      <c r="M15" s="5">
+        <v>33</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1425077.337503433</v>
+      </c>
+      <c r="O15" s="4">
+        <v>231.0436669104139</v>
+      </c>
+      <c r="P15" s="5">
+        <v>6168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D16" s="3">
+        <v>51.51515151515152</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>48.48484848484848</v>
+      </c>
+      <c r="G16" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.8852452227183449</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.3725486616829538</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.6589172293239196</v>
+      </c>
+      <c r="K16" s="4">
+        <v>67.02329416615153</v>
+      </c>
+      <c r="L16" s="4">
+        <v>61.47244254626662</v>
+      </c>
+      <c r="M16" s="5">
+        <v>33</v>
+      </c>
+      <c r="N16" s="5">
+        <v>642422.5540161133</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.44047717071918</v>
+      </c>
+      <c r="P16" s="5">
+        <v>6526</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>63.63636363636363</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="D17" s="3">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15.15151515151515</v>
+      </c>
+      <c r="F17" s="3">
+        <v>18.18181818181818</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.7530857923593304</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2810431483661814</v>
+      </c>
+      <c r="J17" s="4">
+        <v>2.644184965612205</v>
+      </c>
+      <c r="K17" s="4">
+        <v>78.27355184498063</v>
+      </c>
+      <c r="L17" s="4">
+        <v>74.0512507626606</v>
+      </c>
+      <c r="M17" s="5">
+        <v>33</v>
+      </c>
+      <c r="N17" s="5">
+        <v>1087210.937023163</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.6490406427664</v>
+      </c>
+      <c r="P17" s="5">
+        <v>10802</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3206,10 +5374,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
@@ -3382,10 +5550,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -3470,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="5">
         <v>10</v>
@@ -3558,10 +5726,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
@@ -3605,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
@@ -3646,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5">
         <v>11</v>
@@ -3737,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
@@ -3822,10 +5990,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
@@ -3847,9 +6015,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>18</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>5</v>
+      </c>
+      <c r="I3" s="5">
+        <v>5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>14</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>26</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>12</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>9</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>25</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>13</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>26</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>13</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>10</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>23</v>
+      </c>
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5">
+        <v>8</v>
+      </c>
+      <c r="H7" s="5">
+        <v>3</v>
+      </c>
+      <c r="I7" s="5">
+        <v>3</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>11</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>21</v>
+      </c>
+      <c r="C8" s="5">
+        <v>10</v>
+      </c>
+      <c r="D8" s="5">
+        <v>10</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>7</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>3</v>
+      </c>
+      <c r="I9" s="5">
+        <v>3</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>10</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>7</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>18</v>
+      </c>
+      <c r="E11" s="5">
+        <v>5</v>
+      </c>
+      <c r="F11" s="5">
+        <v>13</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>5</v>
+      </c>
+      <c r="I11" s="5">
+        <v>5</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>8</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>21</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5">
+        <v>16</v>
+      </c>
+      <c r="E12" s="5">
+        <v>5</v>
+      </c>
+      <c r="F12" s="5">
+        <v>11</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>5</v>
+      </c>
+      <c r="I12" s="5">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>10</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>14</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>11</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>14</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>14</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>11</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>23</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>7</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>4</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>15</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>17</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>16</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>15</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>21</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>11</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>5</v>
+      </c>
+      <c r="I17" s="5">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6783,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6825,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6856,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>3.201477929548333</v>
@@ -3960,10 +6915,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1884981321435504</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>3.254290563053579</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2028119353246893</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>4.089510006373175</v>
@@ -4001,10 +6974,26 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>4.089510006373175</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.430805407758811</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6813971137589876</v>
@@ -4042,9 +7031,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1168105428810762</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7377132833294215</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1594000027988637</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7062,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7081,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7123,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7154,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5460728051747106</v>
@@ -4173,10 +7213,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1363006975517921</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5145293950315186</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5146190126308887</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2320260492014102</v>
@@ -4214,10 +7272,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2077729077148736</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1540024940559869</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1311624138150983</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.400457637756163</v>
@@ -4255,9 +7331,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.9859454720037514</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5620875780384809</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3277413492563876</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7362,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7381,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7423,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7454,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3537596399276959</v>
@@ -4386,10 +7513,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3002519763490099</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2551718492268957</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.270038712576801</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.9256412068352281</v>
@@ -4427,10 +7572,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.01503207802194311</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.930651899509209</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1359724332840506</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.7305646336788945</v>
@@ -4468,9 +7631,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.07954648878218269</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6774654482479849</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.08376432621854472</v>
+      </c>
+      <c r="R5" s="5">
+        <v>6</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7662,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7681,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7723,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7754,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.9613528002502472</v>
@@ -4599,10 +7813,28 @@
       <c r="M3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.113615899066162</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8847517523705989</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.9766515380729114</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2402760223339647</v>
@@ -4640,10 +7872,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.09175013864905661</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2228722229839361</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1748731003211724</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>1.133713406441621</v>
@@ -4681,9 +7931,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3464528309032904</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9309195811108373</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4809183575292963</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7962,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7981,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8023,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8054,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6024031389953644</v>
@@ -4812,10 +8113,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2295683694738813</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4266288760937451</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.107588213144524</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.579442323898091</v>
@@ -4853,10 +8172,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.1733929253108405</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4987251773509842</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1352515796874911</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>3.810515957324797</v>
@@ -4894,9 +8231,25 @@
       <c r="M5" s="5">
         <v>4</v>
       </c>
+      <c r="N5" s="4">
+        <v>3.272827504746674</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.808455846353154</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8260,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5546534861996736</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.1275346260450798</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2.795487873115705</v>
-      </c>
-      <c r="E3" s="4">
-        <v>71.33928571428571</v>
-      </c>
-      <c r="F3" s="4">
-        <v>67.09731543624162</v>
-      </c>
-      <c r="G3" s="5">
-        <v>16</v>
-      </c>
-      <c r="H3" s="5">
-        <v>8</v>
-      </c>
-      <c r="I3" s="5">
-        <v>6</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.218374692736543</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2209108644879962</v>
-      </c>
-      <c r="D4" s="4">
-        <v>5.028490297993985</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.03854875283518</v>
-      </c>
-      <c r="F4" s="4">
-        <v>68.79194630872642</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>5</v>
-      </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>2</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6788008453607972</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.7522811046844922</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.8429918240920651</v>
-      </c>
-      <c r="E5" s="4">
-        <v>76.56887755102041</v>
-      </c>
-      <c r="F5" s="4">
-        <v>71.24580536912751</v>
-      </c>
-      <c r="G5" s="5">
-        <v>16</v>
-      </c>
-      <c r="H5" s="5">
-        <v>8</v>
-      </c>
-      <c r="I5" s="5">
-        <v>2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>6</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.50729527148986</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6152578854604004</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5727161581137006</v>
-      </c>
-      <c r="E3" s="4">
-        <v>82.66581632653062</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.55914429530202</v>
-      </c>
-      <c r="G3" s="5">
-        <v>16</v>
-      </c>
-      <c r="H3" s="5">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>2</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1892218701600683</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.15473461782067</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.8365301432210228</v>
-      </c>
-      <c r="E4" s="4">
-        <v>74.08541194255454</v>
-      </c>
-      <c r="F4" s="4">
-        <v>72.90206313696191</v>
-      </c>
-      <c r="G4" s="5">
-        <v>9</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>1</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7486654158263883</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4506466197015335</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.298851849519317</v>
-      </c>
-      <c r="E5" s="4">
-        <v>70.66964285714288</v>
-      </c>
-      <c r="F5" s="4">
-        <v>59.70637583892611</v>
-      </c>
-      <c r="G5" s="5">
-        <v>16</v>
-      </c>
-      <c r="H5" s="5">
-        <v>4</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>12</v>
-      </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>10</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/SkafteSelective2019.xlsx
+++ b/public/downloads/SkafteSelective2019.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1275346260450798</v>
+        <v>-0.1074528410191249</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5595526206323549</v>
+        <v>0.5531756084216405</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07356558188790246</v>
+        <v>0.07085244997945117</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.198243643784167</v>
+        <v>-0.1791780964933878</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1911920356718547</v>
+        <v>0.184836853241595</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1185862913919436</v>
+        <v>0.1147731819337878</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -1675,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5224219946696493</v>
+        <v>-0.4932718380098109</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7573665444400008</v>
+        <v>0.7464352356925614</v>
       </c>
       <c r="Q5" s="4">
         <v>0.6031848271278761</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4925250895619714</v>
+        <v>0.203247874527591</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6068917466739844</v>
+        <v>0.5088987962710521</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.657607212986106</v>
+        <v>0.597026682024128</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -1916,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.15473461782067</v>
+        <v>-0.1318312126514058</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1698206083412786</v>
+        <v>0.1672757855446937</v>
       </c>
       <c r="Q4" s="4">
         <v>0.09984362212237367</v>
@@ -2155,16 +2155,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4673762379258266</v>
+        <v>0.4047692303248027</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2242874742260578</v>
+        <v>0.2261767648082181</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.234207870768081</v>
+        <v>0.2306703935437076</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2214,13 +2214,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0869762100861043</v>
+        <v>0.08122282872788844</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2653238145317392</v>
+        <v>0.2646845499363819</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2158392229823131</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>1.06251081608079</v>
+        <v>1.275653194155547</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5510188920913042</v>
+        <v>0.467099931845863</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4836689049295833</v>
+        <v>0.442824417293914</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -2455,16 +2455,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2601089157362083</v>
+        <v>0.328473479388407</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>3.563962218470695</v>
+        <v>3.531595555287173</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.166985305399985</v>
+        <v>0.1562173824976696</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1642231953086252</v>
+        <v>-0.2046746706055274</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>4.533571803942711</v>
+        <v>4.542862210277789</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2068596639187399</v>
+        <v>0.1987693688593595</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2573,16 +2573,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7673232780566241</v>
+        <v>0.8927711560619898</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8147759014379812</v>
+        <v>0.7651905984216283</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6790787479656983</v>
+        <v>0.6522945307202139</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2755,13 +2755,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01423300036377384</v>
+        <v>-0.01379171058593442</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>1.663855293442679</v>
+        <v>1.67436456004882</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1138028825378257</v>
@@ -2814,16 +2814,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.001976872676789298</v>
+        <v>-0.01330847492681642</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>3.002224995403215</v>
+        <v>3.003484062319885</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1620525350124899</v>
+        <v>0.1597862145624845</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2873,13 +2873,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4917722927258001</v>
+        <v>0.4785645539892016</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7369000408108413</v>
+        <v>0.7435039101791405</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3619642073492262</v>
@@ -3055,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1286653207879596</v>
+        <v>-0.09729025054383555</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5994693899731347</v>
+        <v>0.581900104604494</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1050446010107251</v>
+        <v>0.1012811005175678</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -3114,16 +3114,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2236664783896799</v>
+        <v>-0.197211215405332</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2370267869895748</v>
+        <v>0.2340873133246472</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.189961300362479</v>
+        <v>0.1846702477656095</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3173,16 +3173,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3038566337695148</v>
+        <v>0.2634985625268413</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7034498041668624</v>
+        <v>0.7167045258398357</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4777912422967519</v>
+        <v>0.4740321322106933</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -3355,13 +3355,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5665601789473584</v>
+        <v>0.6844261558015887</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4784178210246289</v>
+        <v>0.4342180797042926</v>
       </c>
       <c r="Q3" s="4">
         <v>0.4016437925123739</v>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4118459751901639</v>
+        <v>0.4665670896483221</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3475909820761776</v>
+        <v>0.3415108582474933</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3102260434748837</v>
+        <v>0.299281820583252</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3653,16 +3653,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0921983054230433</v>
+        <v>-0.1234644059569234</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2426243066497177</v>
+        <v>0.2487901192037263</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.198297202818007</v>
+        <v>0.1960962527120586</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -3712,16 +3712,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.8272885743693986</v>
+        <v>-0.8777534162090888</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3230764246175374</v>
+        <v>0.3286836292663919</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1641103523509243</v>
+        <v>0.1569010892309685</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3951,13 +3951,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2667579539594396</v>
+        <v>0.2469956444450645</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9523483333963926</v>
+        <v>0.9474077560177988</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2848334995699222</v>
@@ -4010,16 +4010,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1773509606084815</v>
+        <v>0.1938819832556078</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3151944806798361</v>
+        <v>0.3096841397974607</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2827980120036523</v>
+        <v>0.279491807474227</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -4249,16 +4249,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3725492984602011</v>
+        <v>0.2863285243733742</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2288238386116149</v>
+        <v>0.2320994970283728</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2469265023820767</v>
+        <v>0.234923401031524</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -4308,16 +4308,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3508204352797634</v>
+        <v>-0.3921754454659094</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>1.880759452613775</v>
+        <v>1.894544456009157</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.177889908746015</v>
+        <v>0.1696189067087857</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -4367,16 +4367,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>1.286484203261678</v>
+        <v>1.164297246469289</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5329768320685104</v>
+        <v>0.5541302331224613</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4238652580231612</v>
+        <v>0.4113408071642993</v>
       </c>
       <c r="R5" s="5">
         <v>6</v>
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>2.455552478036258</v>
+        <v>2.451741881056616</v>
       </c>
       <c r="I3" s="4">
         <v>0.2390065072458856</v>
       </c>
       <c r="J3" s="4">
-        <v>4.034094494716774</v>
+        <v>4.026831054220794</v>
       </c>
       <c r="K3" s="4">
         <v>73.96963663514177</v>
@@ -4563,13 +4563,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4539486345274115</v>
+        <v>0.4582839395722174</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3830034136638982</v>
+        <v>0.382512800712651</v>
       </c>
       <c r="J4" s="4">
-        <v>0.7375590147229617</v>
+        <v>0.7457561715819739</v>
       </c>
       <c r="K4" s="4">
         <v>77.34942757590836</v>
@@ -4613,13 +4613,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5682454598824628</v>
+        <v>0.5712081145206888</v>
       </c>
       <c r="I5" s="4">
-        <v>0.1985196039922694</v>
+        <v>0.1984749500077828</v>
       </c>
       <c r="J5" s="4">
-        <v>1.571098460170015</v>
+        <v>1.575671727325507</v>
       </c>
       <c r="K5" s="4">
         <v>76.78944748631179</v>
@@ -4645,13 +4645,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>63.41463414634146</v>
+        <v>58.53658536585365</v>
       </c>
       <c r="C6" s="3">
         <v>4.878048780487805</v>
       </c>
       <c r="D6" s="3">
-        <v>31.70731707317073</v>
+        <v>36.58536585365854</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -4660,16 +4660,16 @@
         <v>31.70731707317073</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>4.878048780487805</v>
       </c>
       <c r="H6" s="4">
-        <v>0.7574778376233756</v>
+        <v>0.6764740420865064</v>
       </c>
       <c r="I6" s="4">
-        <v>0.6390924584244746</v>
+        <v>0.3912228140193535</v>
       </c>
       <c r="J6" s="4">
-        <v>1.309789066683013</v>
+        <v>1.287819712940169</v>
       </c>
       <c r="K6" s="4">
         <v>77.28554836568769</v>
@@ -4713,13 +4713,13 @@
         <v>19.51219512195122</v>
       </c>
       <c r="H7" s="4">
-        <v>1.371948345251445</v>
+        <v>1.370256184055118</v>
       </c>
       <c r="I7" s="4">
         <v>0.1194439416629385</v>
       </c>
       <c r="J7" s="4">
-        <v>3.639662509654689</v>
+        <v>3.638016992760337</v>
       </c>
       <c r="K7" s="4">
         <v>75.65621370499423</v>
@@ -4763,13 +4763,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.555888657614741</v>
+        <v>0.5477391508536973</v>
       </c>
       <c r="I8" s="4">
-        <v>0.2860445109088546</v>
+        <v>0.2841030536441694</v>
       </c>
       <c r="J8" s="4">
-        <v>2.646046105136394</v>
+        <v>2.635256423863968</v>
       </c>
       <c r="K8" s="4">
         <v>73.75311100049855</v>
@@ -4813,13 +4813,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.5662756115872554</v>
+        <v>0.5274758405722265</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4678606712442567</v>
+        <v>0.434816745264996</v>
       </c>
       <c r="J9" s="4">
-        <v>0.9109686107614557</v>
+        <v>0.8924659589322578</v>
       </c>
       <c r="K9" s="4">
         <v>76.10087937614088</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.3608003949234987</v>
+        <v>0.3286484901437252</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3303185548755284</v>
+        <v>0.3125657689315113</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3895822242411092</v>
+        <v>0.358915848572666</v>
       </c>
       <c r="K10" s="4">
         <v>77.26066036170512</v>
@@ -4913,13 +4913,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>2.703950150098127</v>
+        <v>2.674008252483925</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3537731024921364</v>
+        <v>0.3380163876102263</v>
       </c>
       <c r="J11" s="4">
-        <v>4.352247727099993</v>
+        <v>4.314760365353289</v>
       </c>
       <c r="K11" s="4">
         <v>76.3580554172886</v>
@@ -4963,13 +4963,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>1.595905129431348</v>
+        <v>1.602859806939666</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2198285425789935</v>
+        <v>0.2192889424718494</v>
       </c>
       <c r="J12" s="4">
-        <v>3.091377556772224</v>
+        <v>3.102347290821386</v>
       </c>
       <c r="K12" s="4">
         <v>75.98473535755741</v>
@@ -5013,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.560486541198686</v>
+        <v>0.5581575587080756</v>
       </c>
       <c r="I13" s="4">
-        <v>0.2672615832510576</v>
+        <v>0.2631360524121017</v>
       </c>
       <c r="J13" s="4">
-        <v>3.794292500306187</v>
+        <v>3.794713920812981</v>
       </c>
       <c r="K13" s="4">
         <v>73.60876057740143</v>
@@ -5063,13 +5063,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.7425775745049332</v>
+        <v>0.7194891813054322</v>
       </c>
       <c r="I14" s="4">
-        <v>0.5339234964677629</v>
+        <v>0.5308834345534207</v>
       </c>
       <c r="J14" s="4">
-        <v>0.8930753654426814</v>
+        <v>0.8771303647798002</v>
       </c>
       <c r="K14" s="4">
         <v>74.46093588950696</v>
@@ -5113,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.4595376834708365</v>
+        <v>0.4640564059770131</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2548649066677807</v>
+        <v>0.2515224613151255</v>
       </c>
       <c r="J15" s="4">
-        <v>1.515233873547921</v>
+        <v>1.519635296374711</v>
       </c>
       <c r="K15" s="4">
         <v>80.9760874046584</v>
@@ -5163,13 +5163,13 @@
         <v>3.03030303030303</v>
       </c>
       <c r="H16" s="4">
-        <v>0.8852452227183449</v>
+        <v>0.8813469710214092</v>
       </c>
       <c r="I16" s="4">
-        <v>0.3725486616829538</v>
+        <v>0.3714465935064787</v>
       </c>
       <c r="J16" s="4">
-        <v>0.6589172293239196</v>
+        <v>0.6586121248114157</v>
       </c>
       <c r="K16" s="4">
         <v>67.02329416615153</v>
@@ -5213,13 +5213,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.7530857923593304</v>
+        <v>0.7635616339853354</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2810431483661814</v>
+        <v>0.2697796850878554</v>
       </c>
       <c r="J17" s="4">
-        <v>2.644184965612205</v>
+        <v>2.686855906479992</v>
       </c>
       <c r="K17" s="4">
         <v>78.27355184498063</v>
@@ -6234,13 +6234,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="5">
         <v>2</v>
       </c>
       <c r="D6" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5">
         <v>0</v>
@@ -6916,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1884981321435504</v>
+        <v>-0.1645891182177763</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>3.254290563053579</v>
+        <v>3.245324682831414</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2028119353246893</v>
@@ -7032,13 +7032,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1168105428810762</v>
+        <v>-0.1155325036200097</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7377132833294215</v>
+        <v>0.736914508791255</v>
       </c>
       <c r="Q5" s="4">
         <v>0.1594000027988637</v>
@@ -7214,16 +7214,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1363006975517921</v>
+        <v>0.1816375130969448</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5145293950315186</v>
+        <v>0.5137509740614243</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5146190126308887</v>
+        <v>0.5137293886650666</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -7273,16 +7273,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2077729077148736</v>
+        <v>-0.2364889440039519</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1540024940559869</v>
+        <v>0.1571596979535599</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1311624138150983</v>
+        <v>0.1311122136132781</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -7332,13 +7332,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.9859454720037514</v>
+        <v>0.9657220460937026</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5620875780384809</v>
+        <v>0.5721992909935052</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3277413492563876</v>
@@ -7514,13 +7514,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3002519763490099</v>
+        <v>0.2751404415256218</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2551718492268957</v>
+        <v>0.2583107910798192</v>
       </c>
       <c r="Q3" s="4">
         <v>0.270038712576801</v>
@@ -7573,16 +7573,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01503207802194311</v>
+        <v>-0.01614842763410707</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.930651899509209</v>
+        <v>0.9310240160465971</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1359724332840506</v>
+        <v>0.1357491633616178</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7632,13 +7632,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.07954648878218269</v>
+        <v>0.07275681661378286</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6774654482479849</v>
+        <v>0.6817089933532348</v>
       </c>
       <c r="Q5" s="4">
         <v>0.08376432621854472</v>
@@ -7814,22 +7814,22 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>1.113615899066162</v>
+        <v>0.5292451990563904</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8847517523705989</v>
+        <v>0.6240846764282191</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9766515380729114</v>
+        <v>0.4631774929921733</v>
       </c>
       <c r="R3" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="S3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7873,16 +7873,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09175013864905661</v>
+        <v>0.07671905475581298</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2228722229839361</v>
+        <v>0.2211097146549356</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1748731003211724</v>
+        <v>0.1747345184765455</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3464528309032904</v>
+        <v>0.2210076387059985</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.9309195811108373</v>
+        <v>0.9850058419250525</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4809183575292963</v>
+        <v>0.4636456869604348</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -8114,13 +8114,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2295683694738813</v>
+        <v>0.2336547983605897</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4266288760937451</v>
+        <v>0.4245856616503909</v>
       </c>
       <c r="Q3" s="4">
         <v>0.107588213144524</v>
@@ -8173,13 +8173,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1733929253108405</v>
+        <v>0.2100801032665629</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4987251773509842</v>
+        <v>0.4946488242447928</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1352515796874911</v>
@@ -8232,7 +8232,7 @@
         <v>4</v>
       </c>
       <c r="N5" s="4">
-        <v>3.272827504746674</v>
+        <v>3.307100649981059</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
